--- a/inputData/Experiments/inputDataEx10_15_35.xlsx
+++ b/inputData/Experiments/inputDataEx10_15_35.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C4E158-E5E9-4197-A1C8-BB61BBD6A15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2576CE99-7D17-A842-A2E5-A120A8D3B460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>type</t>
   </si>
@@ -146,7 +147,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -537,12 +538,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -550,7 +551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -558,7 +559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -566,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -574,7 +575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -582,7 +583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -590,7 +591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -598,7 +599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -606,7 +607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -614,7 +615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -622,7 +623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -630,7 +631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -638,7 +639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -646,7 +647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -654,7 +655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -662,7 +663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -678,14 +679,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -716,7 +717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -733,7 +734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -750,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -767,7 +768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -784,7 +785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -801,7 +802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -818,7 +819,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -835,7 +836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -852,7 +853,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -869,10 +870,10 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5">
       <c r="E18" s="3"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5">
       <c r="D20" s="3"/>
     </row>
   </sheetData>
@@ -884,13 +885,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X36"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -910,7 +911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -930,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -950,7 +951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -970,7 +971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -990,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1010,7 +1011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1030,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1050,7 +1051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1070,7 +1071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1090,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1110,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1130,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1150,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1190,7 +1191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1210,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1230,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1250,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1270,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1310,7 +1311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1356,7 +1357,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1388,7 +1389,7 @@
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1420,7 +1421,7 @@
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1452,7 +1453,7 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1484,7 +1485,7 @@
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1516,7 +1517,7 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1548,7 +1549,7 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1580,7 +1581,7 @@
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1612,7 +1613,7 @@
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1644,7 +1645,7 @@
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1664,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1684,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1719,6 +1720,736 @@
       </c>
       <c r="E36">
         <v>4</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2774C01F-6E02-E742-A2F9-EAF63A2F419E}">
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>72</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>107</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>96</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>54</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>83</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>46</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>61</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>74</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>33</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>89</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>42</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>105</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>57</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>21</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>92</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>36</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>67</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>9</v>
+      </c>
+      <c r="D24">
+        <v>78</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>49</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>110</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>31</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>64</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>25</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>87</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>58</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32">
+        <v>43</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>19</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
+      <c r="D35">
+        <v>82</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>52</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
       </c>
       <c r="F36">
         <v>0</v>
